--- a/artfynd/A 4226-2026 artfynd.xlsx
+++ b/artfynd/A 4226-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131428209</v>
       </c>
       <c r="B2" t="n">
-        <v>91341</v>
+        <v>91342</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4226-2026 artfynd.xlsx
+++ b/artfynd/A 4226-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131428209</v>
       </c>
       <c r="B2" t="n">
-        <v>91342</v>
+        <v>91345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4226-2026 artfynd.xlsx
+++ b/artfynd/A 4226-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131428209</v>
       </c>
       <c r="B2" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4226-2026 artfynd.xlsx
+++ b/artfynd/A 4226-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131428209</v>
       </c>
       <c r="B2" t="n">
-        <v>91346</v>
+        <v>91352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4226-2026 artfynd.xlsx
+++ b/artfynd/A 4226-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131428209</v>
       </c>
       <c r="B2" t="n">
-        <v>91352</v>
+        <v>91353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4226-2026 artfynd.xlsx
+++ b/artfynd/A 4226-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131428209</v>
       </c>
       <c r="B2" t="n">
-        <v>91353</v>
+        <v>91356</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4226-2026 artfynd.xlsx
+++ b/artfynd/A 4226-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131428209</v>
       </c>
       <c r="B2" t="n">
-        <v>91356</v>
+        <v>91362</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4226-2026 artfynd.xlsx
+++ b/artfynd/A 4226-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131428209</v>
       </c>
       <c r="B2" t="n">
-        <v>91362</v>
+        <v>91365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4226-2026 artfynd.xlsx
+++ b/artfynd/A 4226-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131428209</v>
       </c>
       <c r="B2" t="n">
-        <v>91365</v>
+        <v>91370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4226-2026 artfynd.xlsx
+++ b/artfynd/A 4226-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131428209</v>
+        <v>111811940</v>
       </c>
       <c r="B2" t="n">
-        <v>91370</v>
+        <v>106415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,50 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>233196</v>
+        <v>698</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällfotad fingersvamp</t>
+          <t>Sen fältgentiana</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramaria rufescens</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Corner</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Gentianella campestris var. campestris</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Backvallen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485502</v>
+        <v>485544</v>
       </c>
       <c r="R2" t="n">
-        <v>6991022</v>
+        <v>6990949</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,17 +756,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-09-01</t>
+          <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-09-01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>kalkbarrskog</t>
+          <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,21 +780,124 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131428209</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91433</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>233196</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fjällfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ramaria rufescens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Corner</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Backvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>485502</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6991022</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2017-09-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2017-09-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Pontus Wallén</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Pontus Wallén</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
         </is>

--- a/artfynd/A 4226-2026 artfynd.xlsx
+++ b/artfynd/A 4226-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111811940</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,8 +912,17 @@
           <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131428209</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>